--- a/docs/all/01_TablasDescriptivas/idx6_crecimiento_summary_labels.xlsx
+++ b/docs/all/01_TablasDescriptivas/idx6_crecimiento_summary_labels.xlsx
@@ -433,10 +433,10 @@
         <v>125</v>
       </c>
       <c r="D3">
-        <v>7.630045038223267</v>
+        <v>7.630045038223266</v>
       </c>
       <c r="E3">
-        <v>4.173835608636349</v>
+        <v>4.173835608636351</v>
       </c>
       <c r="F3">
         <v>2.733900308609009</v>
@@ -544,7 +544,7 @@
         <v>0.1006869377218011</v>
       </c>
       <c r="E7">
-        <v>0.1480911592960064</v>
+        <v>0.1480911592960066</v>
       </c>
       <c r="F7">
         <v>0</v>
